--- a/templates/Warehouse_Master_Import_Template.xlsx
+++ b/templates/Warehouse_Master_Import_Template.xlsx
@@ -399,31 +399,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:V10"/>
-  <cols>
-    <col min="1" max="1" width="16.83203125" customWidth="1"/>
-    <col min="2" max="2" width="17.83203125" customWidth="1"/>
-    <col min="3" max="3" width="14.83203125" customWidth="1"/>
-    <col min="4" max="4" width="14.83203125" customWidth="1"/>
-    <col min="5" max="5" width="14.83203125" customWidth="1"/>
-    <col min="6" max="6" width="14.83203125" customWidth="1"/>
-    <col min="7" max="7" width="14.83203125" customWidth="1"/>
-    <col min="8" max="8" width="14.83203125" customWidth="1"/>
-    <col min="9" max="9" width="14.83203125" customWidth="1"/>
-    <col min="10" max="10" width="14.83203125" customWidth="1"/>
-    <col min="11" max="11" width="14.83203125" customWidth="1"/>
-    <col min="12" max="12" width="14.83203125" customWidth="1"/>
-    <col min="13" max="13" width="15.83203125" customWidth="1"/>
-    <col min="14" max="14" width="14.83203125" customWidth="1"/>
-    <col min="15" max="15" width="15.83203125" customWidth="1"/>
-    <col min="16" max="16" width="14.83203125" customWidth="1"/>
-    <col min="17" max="17" width="14.83203125" customWidth="1"/>
-    <col min="18" max="18" width="20.83203125" customWidth="1"/>
-    <col min="19" max="19" width="14.83203125" customWidth="1"/>
-    <col min="20" max="20" width="14.83203125" customWidth="1"/>
-    <col min="21" max="21" width="14.83203125" customWidth="1"/>
-    <col min="22" max="22" width="15.83203125" customWidth="1"/>
-  </cols>
+  <dimension ref="A1:W10"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -457,39 +433,42 @@
         <v>Area sq ft</v>
       </c>
       <c r="K1" t="str">
+        <v>Parking Slots</v>
+      </c>
+      <c r="L1" t="str">
         <v>GSTIN</v>
       </c>
-      <c r="L1" t="str">
+      <c r="M1" t="str">
         <v>Working Days</v>
       </c>
-      <c r="M1" t="str">
+      <c r="N1" t="str">
         <v>Working Hours</v>
       </c>
-      <c r="N1" t="str">
+      <c r="O1" t="str">
         <v>Contact Name</v>
       </c>
-      <c r="O1" t="str">
+      <c r="P1" t="str">
         <v>Contact Phone</v>
       </c>
-      <c r="P1" t="str">
+      <c r="Q1" t="str">
         <v>Storage Type</v>
       </c>
-      <c r="Q1" t="str">
+      <c r="R1" t="str">
         <v>Category</v>
       </c>
-      <c r="R1" t="str">
+      <c r="S1" t="str">
         <v>Pallet Positions *</v>
       </c>
-      <c r="S1" t="str">
+      <c r="T1" t="str">
         <v>Dim L (m)</v>
       </c>
-      <c r="T1" t="str">
+      <c r="U1" t="str">
         <v>Dim W (m)</v>
       </c>
-      <c r="U1" t="str">
+      <c r="V1" t="str">
         <v>Dim H (m)</v>
       </c>
-      <c r="V1" t="str">
+      <c r="W1" t="str">
         <v>Dispatch Flow</v>
       </c>
     </row>
@@ -524,40 +503,43 @@
       <c r="J2">
         <v>25000</v>
       </c>
-      <c r="K2" t="str">
+      <c r="K2">
+        <v>20</v>
+      </c>
+      <c r="L2" t="str">
         <v>33AAAAA0000A1Z5</v>
       </c>
-      <c r="L2" t="str">
+      <c r="M2" t="str">
         <v>Mon-Sat</v>
       </c>
-      <c r="M2" t="str">
+      <c r="N2" t="str">
         <v>09:00-19:00</v>
       </c>
-      <c r="N2" t="str">
+      <c r="O2" t="str">
         <v>Site Contact</v>
       </c>
-      <c r="O2" t="str">
+      <c r="P2" t="str">
         <v>9876500000</v>
       </c>
-      <c r="P2" t="str">
+      <c r="Q2" t="str">
         <v>SPR</v>
       </c>
-      <c r="Q2" t="str">
+      <c r="R2" t="str">
         <v>Car Tyres</v>
       </c>
-      <c r="R2">
+      <c r="S2">
         <v>3000</v>
       </c>
-      <c r="S2">
+      <c r="T2">
         <v>1</v>
       </c>
-      <c r="T2">
+      <c r="U2">
         <v>1.5</v>
       </c>
-      <c r="U2">
+      <c r="V2">
         <v>1</v>
       </c>
-      <c r="V2" t="str">
+      <c r="W2" t="str">
         <v>Full Pallet</v>
       </c>
     </row>
@@ -608,24 +590,27 @@
         <v/>
       </c>
       <c r="P3" t="str">
+        <v/>
+      </c>
+      <c r="Q3" t="str">
         <v>Drive-in</v>
       </c>
-      <c r="Q3" t="str">
+      <c r="R3" t="str">
         <v>Truck Tyres-Radial</v>
       </c>
-      <c r="R3">
+      <c r="S3">
         <v>1200</v>
       </c>
-      <c r="S3">
+      <c r="T3">
         <v>1.5</v>
       </c>
-      <c r="T3">
+      <c r="U3">
         <v>1.8</v>
       </c>
-      <c r="U3">
+      <c r="V3">
         <v>1.2</v>
       </c>
-      <c r="V3" t="str">
+      <c r="W3" t="str">
         <v>Case Pick</v>
       </c>
     </row>
@@ -694,6 +679,9 @@
         <v/>
       </c>
       <c r="V4" t="str">
+        <v/>
+      </c>
+      <c r="W4" t="str">
         <v>Broken Case</v>
       </c>
     </row>
@@ -764,6 +752,9 @@
       <c r="V5" t="str">
         <v/>
       </c>
+      <c r="W5" t="str">
+        <v/>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
@@ -812,17 +803,17 @@
         <v/>
       </c>
       <c r="P6" t="str">
+        <v/>
+      </c>
+      <c r="Q6" t="str">
         <v>Mix</v>
       </c>
-      <c r="Q6" t="str">
+      <c r="R6" t="str">
         <v>Uncategorized</v>
       </c>
-      <c r="R6">
+      <c r="S6">
         <v>5000</v>
       </c>
-      <c r="S6" t="str">
-        <v/>
-      </c>
       <c r="T6" t="str">
         <v/>
       </c>
@@ -830,6 +821,9 @@
         <v/>
       </c>
       <c r="V6" t="str">
+        <v/>
+      </c>
+      <c r="W6" t="str">
         <v>Full Pallet</v>
       </c>
     </row>
@@ -898,6 +892,9 @@
         <v/>
       </c>
       <c r="V7" t="str">
+        <v/>
+      </c>
+      <c r="W7" t="str">
         <v>Case Pick</v>
       </c>
     </row>
@@ -933,39 +930,42 @@
         <v>40000</v>
       </c>
       <c r="K8" t="str">
+        <v/>
+      </c>
+      <c r="L8" t="str">
         <v>33BBBBB1111B2Z6</v>
-      </c>
-      <c r="L8" t="str">
-        <v>24x7</v>
       </c>
       <c r="M8" t="str">
         <v>24x7</v>
       </c>
       <c r="N8" t="str">
+        <v>24x7</v>
+      </c>
+      <c r="O8" t="str">
         <v>Plant Manager</v>
       </c>
-      <c r="O8" t="str">
+      <c r="P8" t="str">
         <v>9876511111</v>
       </c>
-      <c r="P8" t="str">
+      <c r="Q8" t="str">
         <v>ASRS</v>
       </c>
-      <c r="Q8" t="str">
+      <c r="R8" t="str">
         <v>Water</v>
       </c>
-      <c r="R8">
+      <c r="S8">
         <v>8000</v>
       </c>
-      <c r="S8">
+      <c r="T8">
         <v>0.4</v>
       </c>
-      <c r="T8">
+      <c r="U8">
         <v>0.3</v>
       </c>
-      <c r="U8">
+      <c r="V8">
         <v>0.25</v>
       </c>
-      <c r="V8" t="str">
+      <c r="W8" t="str">
         <v>Full Pallet</v>
       </c>
     </row>
@@ -1016,17 +1016,17 @@
         <v/>
       </c>
       <c r="P9" t="str">
+        <v/>
+      </c>
+      <c r="Q9" t="str">
         <v>Ground/Floor</v>
       </c>
-      <c r="Q9" t="str">
+      <c r="R9" t="str">
         <v>Carbonated</v>
       </c>
-      <c r="R9">
+      <c r="S9">
         <v>2000</v>
       </c>
-      <c r="S9" t="str">
-        <v/>
-      </c>
       <c r="T9" t="str">
         <v/>
       </c>
@@ -1034,6 +1034,9 @@
         <v/>
       </c>
       <c r="V9" t="str">
+        <v/>
+      </c>
+      <c r="W9" t="str">
         <v/>
       </c>
     </row>
@@ -1102,12 +1105,15 @@
         <v/>
       </c>
       <c r="V10" t="str">
+        <v/>
+      </c>
+      <c r="W10" t="str">
         <v>Full Pallet</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:V10"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:W10"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -1115,9 +1121,6 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:A13"/>
-  <cols>
-    <col min="1" max="1" width="100.83203125" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1193,12 +1196,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C20"/>
-  <cols>
-    <col min="1" max="1" width="28.83203125" customWidth="1"/>
-    <col min="2" max="2" width="32.83203125" customWidth="1"/>
-    <col min="3" max="3" width="100.83203125" customWidth="1"/>
-  </cols>
+  <dimension ref="A1:C21"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1312,117 +1310,128 @@
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>GSTIN</v>
+        <v>Parking Slots</v>
       </c>
       <c r="B11" t="str">
         <v>No</v>
       </c>
       <c r="C11" t="str">
-        <v>This facility's own GST registration number — distinct from any customer's GST number. No format enforced yet.</v>
+        <v>Whole number, 0 or more — how many vehicles can park in the yard at once. Generates that many numbered parking slots for this warehouse (Y1, Y2...). Leave blank/0 for a facility with no on-site parking — Yard Management simply does not apply to it.</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>Working Days</v>
+        <v>GSTIN</v>
       </c>
       <c r="B12" t="str">
         <v>No</v>
       </c>
       <c r="C12" t="str">
-        <v>Free text, e.g. "Mon-Sat" or "24x7".</v>
+        <v>This facility's own GST registration number — distinct from any customer's GST number. No format enforced yet.</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>Working Hours</v>
+        <v>Working Days</v>
       </c>
       <c r="B13" t="str">
         <v>No</v>
       </c>
       <c r="C13" t="str">
-        <v>Free text, e.g. "09:00-18:00" or "24x7".</v>
+        <v>Free text, e.g. "Mon-Sat" or "24x7".</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>Contact Name</v>
+        <v>Working Hours</v>
       </c>
       <c r="B14" t="str">
         <v>No</v>
       </c>
       <c r="C14" t="str">
-        <v>Free text — the facility's primary point of contact.</v>
+        <v>Free text, e.g. "09:00-18:00" or "24x7".</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>Contact Phone</v>
+        <v>Contact Name</v>
       </c>
       <c r="B15" t="str">
         <v>No</v>
       </c>
       <c r="C15" t="str">
-        <v>Free text.</v>
+        <v>Free text — the facility's primary point of contact.</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>Storage Type</v>
+        <v>Contact Phone</v>
       </c>
       <c r="B16" t="str">
         <v>No</v>
       </c>
       <c r="C16" t="str">
-        <v>One of: Ground/Floor, SPR, Drive-in, Mix, ASRS. Fill on a row to record one storage-type entry for this warehouse — use multiple rows (same Location Code) to break a warehouse down by storage type, each with its own Category, Pallet Positions, and dimensions. Don't combine "Mix" with specific storage-type rows for the same warehouse — pick one approach per warehouse.</v>
+        <v>Free text.</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>Category</v>
+        <v>Storage Type</v>
       </c>
       <c r="B17" t="str">
         <v>No</v>
       </c>
       <c r="C17" t="str">
-        <v>Must match a name in the Product Category master list (case-insensitive). Leave blank for "Uncategorized". This list is centrally managed — ask before typing a new category name, it will be rejected if not found. The same Category can appear against more than one Storage Type on the same warehouse (different Pallet count/dimensions each); what's not allowed is the same Storage Type + Category pair twice.</v>
+        <v>One of: Ground/Floor, SPR, Drive-in, Mix, ASRS. Fill on a row to record one storage-type entry for this warehouse — use multiple rows (same Location Code) to break a warehouse down by storage type, each with its own Category, Pallet Positions, and dimensions. Don't combine "Mix" with specific storage-type rows for the same warehouse — pick one approach per warehouse.</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>Pallet Positions *</v>
+        <v>Category</v>
       </c>
       <c r="B18" t="str">
-        <v>Only if Storage Type is filled on that row</v>
+        <v>No</v>
       </c>
       <c r="C18" t="str">
-        <v>Whole number, the pallet capacity for that specific Storage Type + Category combination (or the total, if using "Mix").</v>
+        <v>Must match a name in the Product Category master list (case-insensitive). Leave blank for "Uncategorized". This list is centrally managed — ask before typing a new category name, it will be rejected if not found. The same Category can appear against more than one Storage Type on the same warehouse (different Pallet count/dimensions each); what's not allowed is the same Storage Type + Category pair twice.</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>Dim L (m) / Dim W (m) / Dim H (m)</v>
+        <v>Pallet Positions *</v>
       </c>
       <c r="B19" t="str">
-        <v>No</v>
+        <v>Only if Storage Type is filled on that row</v>
       </c>
       <c r="C19" t="str">
-        <v>Positive numbers, in meters — the pallet-position dimensions for this Storage Type + Category combination. Optional; leave blank if not measured yet.</v>
+        <v>Whole number, the pallet capacity for that specific Storage Type + Category combination (or the total, if using "Mix").</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>Dispatch Flow</v>
+        <v>Dim L (m) / Dim W (m) / Dim H (m)</v>
       </c>
       <c r="B20" t="str">
         <v>No</v>
       </c>
       <c r="C20" t="str">
+        <v>Positive numbers, in meters — the pallet-position dimensions for this Storage Type + Category combination. Optional; leave blank if not measured yet.</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="str">
+        <v>Dispatch Flow</v>
+      </c>
+      <c r="B21" t="str">
+        <v>No</v>
+      </c>
+      <c r="C21" t="str">
         <v>One of: Full Pallet, Case Pick, Broken Case. Fill on a row to record one dispatch capability for this warehouse — use multiple rows (same Location Code) to list more than one. A row can carry a Storage Type entry and a Dispatch Flow entry at the same time if convenient, or just one — they're independent, not linked to each other.</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C20"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C21"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/templates/Warehouse_Master_Import_Template.xlsx
+++ b/templates/Warehouse_Master_Import_Template.xlsx
@@ -427,7 +427,7 @@
         <v>3PL Name</v>
       </c>
       <c r="I1" t="str">
-        <v>No of Docks</v>
+        <v>No of Docks *</v>
       </c>
       <c r="J1" t="str">
         <v>Area sq ft</v>
@@ -710,8 +710,8 @@
       <c r="H5" t="str">
         <v/>
       </c>
-      <c r="I5" t="str">
-        <v/>
+      <c r="I5">
+        <v>2</v>
       </c>
       <c r="J5" t="str">
         <v/>
@@ -781,8 +781,8 @@
       <c r="H6" t="str">
         <v/>
       </c>
-      <c r="I6" t="str">
-        <v/>
+      <c r="I6">
+        <v>3</v>
       </c>
       <c r="J6" t="str">
         <v/>
@@ -1120,7 +1120,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A13"/>
+  <dimension ref="A1:A14"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1149,7 +1149,7 @@
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>2. Warehouse-level columns (Type of Node, City Name, Address, Pincode, Latitude, Longitude, 3PL Name, No of Docks, Area sq ft, GSTIN, Working Days, Working Hours, Contact Name, Contact Phone) only need to be filled on the FIRST row of each Location Code group — leave them blank on the rest. Of these, Type of Node, City Name, Address, and Pincode are required on that first row.</v>
+        <v>2. Warehouse-level columns (Type of Node, City Name, Address, Pincode, Latitude, Longitude, 3PL Name, No of Docks, Area sq ft, GSTIN, Working Days, Working Hours, Contact Name, Contact Phone) only need to be filled on the FIRST row of each Location Code group — leave them blank on the rest. Of these, Type of Node, City Name, Address, Pincode, and No of Docks are required on that first row.</v>
       </c>
     </row>
     <row r="7">
@@ -1187,9 +1187,14 @@
         <v>9. See the "Legend &amp; Rules" tab for full per-column validation rules.</v>
       </c>
     </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>10. No of Docks automatically creates that many Dock Doors for this warehouse, each with its own Inbound and Outbound staging bin (named "Dock1-SA-IB"/"Dock1-SA-OB", etc.) — nothing further to set up manually for this.</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:A13"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:A14"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -1288,13 +1293,13 @@
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>No of Docks</v>
+        <v>No of Docks *</v>
       </c>
       <c r="B9" t="str">
-        <v>No</v>
+        <v>Yes, first row</v>
       </c>
       <c r="C9" t="str">
-        <v>Whole number.</v>
+        <v>Whole number, 1 or more. Automatically creates that many Dock Doors for this warehouse, each with its own auto-named Inbound ("Dock{N}-SA-IB") and Outbound ("Dock{N}-SA-OB") staging Location — no manual Dock Door or staging setup needed.</v>
       </c>
     </row>
     <row r="10">
